--- a/output/pdf_financials_xlsx/BIGT.xlsx
+++ b/output/pdf_financials_xlsx/BIGT.xlsx
@@ -1273,13 +1273,13 @@
         <v>-2.454458</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.997702</v>
+        <v>-1.997702</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.169321</v>
+        <v>-0.169321</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.04793</v>
+        <v>-1.04793</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.149663</v>
@@ -1297,13 +1297,13 @@
         <v>-0.198769</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.124469</v>
+        <v>-2.124469</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.64738</v>
+        <v>-0.64738</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.312992</v>
+        <v>-0.312992</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-0.298608</v>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.681046</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-2.371086</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.840523</v>
+        <v>-2.840523</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.366586</v>
+        <v>-2.366586</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.312285</v>
@@ -1573,13 +1573,13 @@
         <v>-1.227229</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.997702</v>
+        <v>-1.997702</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.169321</v>
+        <v>-0.169321</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.04793</v>
+        <v>-1.04793</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.149663</v>
@@ -1597,13 +1597,13 @@
         <v>-0.198769</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.124469</v>
+        <v>-2.124469</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.64738</v>
+        <v>-0.64738</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.312992</v>
+        <v>-0.312992</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>-0.298608</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.840523</v>
+        <v>-2.840523</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.366586</v>
+        <v>-2.366586</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.312285</v>
@@ -1747,13 +1747,13 @@
         <v>-1.227229</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.997702</v>
+        <v>-1.997702</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.169321</v>
+        <v>-0.169321</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.04793</v>
+        <v>-1.04793</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.149663</v>
@@ -1771,13 +1771,13 @@
         <v>-0.198769</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.124469</v>
+        <v>-2.124469</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.64738</v>
+        <v>-0.64738</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.312992</v>
+        <v>-0.312992</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>-0.298608</v>
@@ -2081,13 +2081,13 @@
         <v>-2.454458</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.997702</v>
+        <v>-1.997702</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.169321</v>
+        <v>-0.169321</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.04793</v>
+        <v>-1.04793</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.149663</v>
@@ -2105,13 +2105,13 @@
         <v>-0.198769</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.124469</v>
+        <v>-2.124469</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.64738</v>
+        <v>-0.64738</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.312992</v>
+        <v>-0.312992</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.298608</v>
@@ -2197,13 +2197,13 @@
         <v>-2.454001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.998799</v>
+        <v>-1.996605</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.169961</v>
+        <v>-0.168681</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.04793</v>
+        <v>-1.04793</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.149663</v>
@@ -2221,13 +2221,13 @@
         <v>-0.198769</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.124469</v>
+        <v>-2.124469</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.64738</v>
+        <v>-0.64738</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.312992</v>
+        <v>-0.312992</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.298608</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>100</v>
@@ -2347,13 +2347,13 @@
         <v>-50</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -2371,13 +2371,13 @@
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0</v>
@@ -43668,10 +43668,10 @@
         </is>
       </c>
       <c r="S353" s="5" t="n">
-        <v>0.312992</v>
+        <v>-0.312992</v>
       </c>
       <c r="T353" s="5" t="n">
-        <v>0.298608</v>
+        <v>-0.298608</v>
       </c>
       <c r="U353" t="inlineStr">
         <is>
@@ -44630,13 +44630,13 @@
         </is>
       </c>
       <c r="Q363" s="5" t="n">
-        <v>2.124469</v>
+        <v>-2.124469</v>
       </c>
       <c r="R363" s="5" t="n">
-        <v>0.64738</v>
+        <v>-0.64738</v>
       </c>
       <c r="S363" s="5" t="n">
-        <v>1.085494</v>
+        <v>-1.085494</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -46284,13 +46284,13 @@
         </is>
       </c>
       <c r="J380" s="5" t="n">
-        <v>0.169321</v>
+        <v>-0.169321</v>
       </c>
       <c r="K380" s="5" t="n">
-        <v>1.04793</v>
+        <v>-1.04793</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>0.149663</v>
+        <v>-0.149663</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
@@ -48948,10 +48948,10 @@
         </is>
       </c>
       <c r="E407" s="5" t="n">
-        <v>2.840523</v>
+        <v>-2.840523</v>
       </c>
       <c r="F407" s="5" t="n">
-        <v>2.366586</v>
+        <v>-2.366586</v>
       </c>
       <c r="G407" s="5" t="n">
         <v>-1.312285</v>
@@ -48960,10 +48960,10 @@
         <v>-1.227229</v>
       </c>
       <c r="I407" s="5" t="n">
-        <v>1.997702</v>
+        <v>-1.997702</v>
       </c>
       <c r="J407" s="5" t="n">
-        <v>0.169321</v>
+        <v>-0.169321</v>
       </c>
       <c r="K407" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BIGT.xlsx
+++ b/output/pdf_financials_xlsx/BIGT.xlsx
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.076532</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000373</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-1.8e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1068,16 +1068,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.063003</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0645</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.038105</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035063</v>
       </c>
     </row>
     <row r="13">
@@ -2069,13 +2069,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.840523</v>
+        <v>2.917055</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.371086</v>
+        <v>2.371459</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.33157</v>
+        <v>-3.331552</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.454458</v>
@@ -2108,16 +2108,16 @@
         <v>-2.124469</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.64738</v>
+        <v>-0.584377</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.312992</v>
+        <v>-0.248492</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.298608</v>
+        <v>-0.260503</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.347548</v>
+        <v>-0.312485</v>
       </c>
     </row>
     <row r="28">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.846121</v>
+        <v>2.922653</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.371086</v>
+        <v>2.371459</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.33157</v>
+        <v>-3.331552</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.454001</v>
@@ -2224,16 +2224,16 @@
         <v>-2.124469</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.64738</v>
+        <v>-0.584377</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.312992</v>
+        <v>-0.248492</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.298608</v>
+        <v>-0.260503</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.347548</v>
+        <v>-0.312485</v>
       </c>
     </row>
     <row r="30">
@@ -42681,7 +42681,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -44261,7 +44261,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -45158,7 +45158,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -50538,7 +50538,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E423" s="5" t="n">

--- a/output/pdf_financials_xlsx/BIGT.xlsx
+++ b/output/pdf_financials_xlsx/BIGT.xlsx
@@ -3811,13 +3811,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.002194</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>0.08773300000000001</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>0.089213</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0</v>
@@ -3869,13 +3869,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.000457</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.018123</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.018763</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.02875</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7284,22 +7284,22 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.052373</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.02377</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.021655</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.052661</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -20447,7 +20447,11 @@
           <t>Proceeds from private placement (note 8)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -20649,7 +20653,11 @@
           <t>Proceeds from the sale of marketable securities (note 5)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -22039,7 +22047,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22540,7 +22552,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -26643,7 +26659,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -28158,7 +28178,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -38229,7 +38253,11 @@
           <t>Future income tax recoveries</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -39132,7 +39160,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -40740,7 +40772,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -41455,7 +41491,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
